--- a/assets/data/capcollection.xlsx
+++ b/assets/data/capcollection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\BottleCapCollection\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C6C669-D16E-4B59-AAD2-AC5EE9C7B5D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB5EB31-0257-4AC1-AB5A-EDBC90A9BDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="361">
   <si>
     <t>FONT D'OR</t>
   </si>
@@ -109,9 +109,6 @@
     <t>WARSTEINER (pilsener)</t>
   </si>
   <si>
-    <t>LA SEU BELLA</t>
-  </si>
-  <si>
     <t>BIRRA MORETTI 
 (1859 premium lager)</t>
   </si>
@@ -252,9 +249,6 @@
     <t>PERONI (birra roma)</t>
   </si>
   <si>
-    <t>STEINBURG (8419 9669)</t>
-  </si>
-  <si>
     <t>KÖSTRITZER (Kirsche)</t>
   </si>
   <si>
@@ -1057,6 +1051,84 @@
   </si>
   <si>
     <t>DAYAO (奖)</t>
+  </si>
+  <si>
+    <t>LA SEU BELLA (blat)</t>
+  </si>
+  <si>
+    <t>LA SEU BELLA (blat) v2</t>
+  </si>
+  <si>
+    <t>xapa negra</t>
+  </si>
+  <si>
+    <t>xapa blanca</t>
+  </si>
+  <si>
+    <t>xapa roja</t>
+  </si>
+  <si>
+    <t>image164.png</t>
+  </si>
+  <si>
+    <t>image165.png</t>
+  </si>
+  <si>
+    <t>image166.png</t>
+  </si>
+  <si>
+    <t>image167.png</t>
+  </si>
+  <si>
+    <t>image168.png</t>
+  </si>
+  <si>
+    <t>image169.png</t>
+  </si>
+  <si>
+    <t>image170.png</t>
+  </si>
+  <si>
+    <t>image171.png</t>
+  </si>
+  <si>
+    <t>image172.png</t>
+  </si>
+  <si>
+    <t>BACILLI</t>
+  </si>
+  <si>
+    <t>STAROBRNO (medium)</t>
+  </si>
+  <si>
+    <t>UR-KROSTITZER (feinherbes pilsner)</t>
+  </si>
+  <si>
+    <t>MUFLON</t>
+  </si>
+  <si>
+    <t>KOZEL (11)</t>
+  </si>
+  <si>
+    <t>PILSNER URQUELL</t>
+  </si>
+  <si>
+    <t>KRUSOVICE (10)</t>
+  </si>
+  <si>
+    <t>MĚŠTANSKÝ PIVOVAR (12%)</t>
+  </si>
+  <si>
+    <t>MĚŠTANSKÝ PIVOVAR (10%)</t>
+  </si>
+  <si>
+    <t>STEINBURG (clasica)</t>
+  </si>
+  <si>
+    <t>image173.png</t>
+  </si>
+  <si>
+    <t>SVIJANY (maz)</t>
   </si>
 </sst>
 </file>
@@ -1136,7 +1208,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1174,11 +1246,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1218,6 +1303,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1540,16 +1631,16 @@
   <sheetData>
     <row r="1" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -1584,7 +1675,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -1620,7 +1711,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1656,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -1692,7 +1783,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -1728,7 +1819,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1764,7 +1855,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -1800,7 +1891,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -1836,7 +1927,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1872,7 +1963,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1908,7 +1999,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -1944,7 +2035,7 @@
         <v>13</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -1980,7 +2071,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -2016,7 +2107,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -2051,7 +2142,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -2087,7 +2178,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -2123,7 +2214,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -2159,7 +2250,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -2195,7 +2286,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -2231,7 +2322,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -2261,13 +2352,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -2296,15 +2387,17 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>28</v>
+        <v>335</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="E22" s="3"/>
+        <v>280</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>339</v>
+      </c>
       <c r="F22" s="3"/>
       <c r="G22" s="6"/>
       <c r="H22" s="6"/>
@@ -2332,13 +2425,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -2368,13 +2461,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -2404,13 +2497,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -2440,13 +2533,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -2476,13 +2569,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -2512,13 +2605,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -2548,13 +2641,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -2584,13 +2677,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -2620,13 +2713,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -2656,13 +2749,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -2698,7 +2791,7 @@
         <v>11</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2728,13 +2821,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2764,13 +2857,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2800,13 +2893,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2836,13 +2929,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -2872,13 +2965,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2908,13 +3001,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -2944,13 +3037,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -2980,13 +3073,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -3016,13 +3109,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -3052,13 +3145,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -3088,13 +3181,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -3130,7 +3223,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -3160,15 +3253,17 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>28</v>
+        <v>336</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="E46" s="3"/>
+        <v>280</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>337</v>
+      </c>
       <c r="F46" s="3"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
@@ -3196,13 +3291,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -3232,13 +3327,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -3268,13 +3363,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -3304,13 +3399,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -3340,13 +3435,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -3376,13 +3471,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -3412,13 +3507,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -3448,13 +3543,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -3484,13 +3579,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -3520,13 +3615,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -3556,13 +3651,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -3592,13 +3687,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -3628,13 +3723,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -3664,13 +3759,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -3700,13 +3795,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
@@ -3736,13 +3831,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
@@ -3772,13 +3867,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -3808,13 +3903,13 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C64" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -3844,13 +3939,13 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
@@ -3880,13 +3975,13 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
@@ -3916,13 +4011,13 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -3952,13 +4047,13 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -3987,13 +4082,13 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
@@ -4022,13 +4117,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C70" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
@@ -4058,13 +4153,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -4094,13 +4189,13 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -4130,13 +4225,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -4165,13 +4260,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -4201,13 +4296,13 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -4237,15 +4332,17 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="E76" s="3"/>
+        <v>280</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>338</v>
+      </c>
       <c r="F76" s="3"/>
       <c r="G76" s="6"/>
       <c r="H76" s="6"/>
@@ -4273,13 +4370,13 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -4309,13 +4406,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -4345,13 +4442,13 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -4381,13 +4478,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -4417,13 +4514,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C81" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -4453,13 +4550,13 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C82" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
@@ -4489,13 +4586,13 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -4525,13 +4622,13 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C84" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -4561,13 +4658,13 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -4597,13 +4694,13 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C86" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
@@ -4633,13 +4730,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C87" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -4669,13 +4766,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -4705,13 +4802,13 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C89" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -4741,13 +4838,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -4777,13 +4874,13 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -4813,13 +4910,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
@@ -4849,13 +4946,13 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C93" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
@@ -4885,13 +4982,13 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
@@ -4921,13 +5018,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
@@ -4957,13 +5054,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
@@ -4993,13 +5090,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
@@ -5029,13 +5126,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>72</v>
+        <v>358</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
@@ -5065,13 +5162,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
@@ -5101,13 +5198,13 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
@@ -5137,13 +5234,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
@@ -5173,13 +5270,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
@@ -5209,13 +5306,13 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
@@ -5245,13 +5342,13 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C104" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
@@ -5286,7 +5383,7 @@
         <v>1</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
@@ -5321,7 +5418,7 @@
         <v>1</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
@@ -5350,13 +5447,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
@@ -5386,13 +5483,13 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C108" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
@@ -5422,13 +5519,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
@@ -5458,13 +5555,13 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
@@ -5499,7 +5596,7 @@
         <v>1</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
@@ -5529,13 +5626,13 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
@@ -5565,13 +5662,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
@@ -5601,13 +5698,13 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
@@ -5637,13 +5734,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
@@ -5673,13 +5770,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
@@ -5709,13 +5806,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
@@ -5745,13 +5842,13 @@
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
@@ -5781,13 +5878,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
@@ -5817,13 +5914,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
@@ -5853,13 +5950,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
@@ -5889,13 +5986,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
@@ -5925,13 +6022,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
@@ -5961,13 +6058,13 @@
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
@@ -6003,7 +6100,7 @@
         <v>1</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
@@ -6033,13 +6130,13 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
@@ -6069,13 +6166,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
@@ -6105,13 +6202,13 @@
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
@@ -6140,13 +6237,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
@@ -6176,13 +6273,13 @@
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
@@ -6212,13 +6309,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
@@ -6248,13 +6345,13 @@
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
@@ -6284,13 +6381,13 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
@@ -6320,13 +6417,13 @@
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
@@ -6356,13 +6453,13 @@
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
@@ -6392,13 +6489,13 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
@@ -6428,13 +6525,13 @@
         <v>136</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
@@ -6464,13 +6561,13 @@
         <v>137</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
@@ -6500,13 +6597,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
@@ -6536,13 +6633,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="D140" s="5" t="s">
         <v>279</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>281</v>
       </c>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
@@ -6572,13 +6669,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
@@ -6608,13 +6705,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
@@ -6644,13 +6741,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
@@ -6680,13 +6777,13 @@
         <v>143</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
@@ -6716,13 +6813,13 @@
         <v>144</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
@@ -6752,13 +6849,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
@@ -6788,13 +6885,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
@@ -6824,13 +6921,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
@@ -6860,13 +6957,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
@@ -6896,13 +6993,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
@@ -6932,13 +7029,13 @@
         <v>150</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
@@ -6968,13 +7065,13 @@
         <v>151</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
@@ -7004,13 +7101,13 @@
         <v>152</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
@@ -7040,13 +7137,13 @@
         <v>153</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E154" s="3"/>
       <c r="F154" s="12"/>
@@ -7076,13 +7173,13 @@
         <v>154</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
@@ -7112,13 +7209,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
@@ -7148,13 +7245,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
@@ -7184,13 +7281,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
@@ -7220,13 +7317,13 @@
         <v>158</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
@@ -7256,13 +7353,13 @@
         <v>159</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
@@ -7292,13 +7389,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
@@ -7328,13 +7425,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
@@ -7364,13 +7461,13 @@
         <v>162</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
@@ -7399,14 +7496,14 @@
       <c r="A164" s="1">
         <v>163</v>
       </c>
-      <c r="B164" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="C164" s="4" t="s">
+      <c r="B164" s="14" t="s">
+        <v>330</v>
+      </c>
+      <c r="C164" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="D164" s="5" t="s">
-        <v>329</v>
+      <c r="D164" s="15" t="s">
+        <v>327</v>
       </c>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
@@ -7432,10 +7529,18 @@
       <c r="Z164" s="3"/>
     </row>
     <row r="165" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="1"/>
-      <c r="B165" s="3"/>
-      <c r="C165" s="3"/>
-      <c r="D165" s="3"/>
+      <c r="A165" s="1">
+        <v>164</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>340</v>
+      </c>
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
       <c r="G165" s="3"/>
@@ -7460,10 +7565,18 @@
       <c r="Z165" s="3"/>
     </row>
     <row r="166" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="1"/>
-      <c r="B166" s="3"/>
-      <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
+      <c r="A166" s="1">
+        <v>165</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D166" s="5" t="s">
+        <v>341</v>
+      </c>
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
       <c r="G166" s="3"/>
@@ -7488,10 +7601,18 @@
       <c r="Z166" s="3"/>
     </row>
     <row r="167" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="1"/>
-      <c r="B167" s="3"/>
-      <c r="C167" s="3"/>
-      <c r="D167" s="3"/>
+      <c r="A167" s="1">
+        <v>166</v>
+      </c>
+      <c r="B167" s="14" t="s">
+        <v>349</v>
+      </c>
+      <c r="C167" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D167" s="15" t="s">
+        <v>342</v>
+      </c>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
       <c r="G167" s="3"/>
@@ -7516,10 +7637,18 @@
       <c r="Z167" s="3"/>
     </row>
     <row r="168" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="1"/>
-      <c r="B168" s="3"/>
-      <c r="C168" s="3"/>
-      <c r="D168" s="3"/>
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D168" s="5" t="s">
+        <v>343</v>
+      </c>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="3"/>
@@ -7544,10 +7673,18 @@
       <c r="Z168" s="3"/>
     </row>
     <row r="169" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="1"/>
-      <c r="B169" s="3"/>
-      <c r="C169" s="3"/>
-      <c r="D169" s="3"/>
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D169" s="5" t="s">
+        <v>344</v>
+      </c>
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
       <c r="G169" s="3"/>
@@ -7572,10 +7709,18 @@
       <c r="Z169" s="3"/>
     </row>
     <row r="170" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="1"/>
-      <c r="B170" s="3"/>
-      <c r="C170" s="3"/>
-      <c r="D170" s="3"/>
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="C170" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D170" s="15" t="s">
+        <v>345</v>
+      </c>
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
       <c r="G170" s="3"/>
@@ -7600,10 +7745,18 @@
       <c r="Z170" s="3"/>
     </row>
     <row r="171" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="3"/>
-      <c r="B171" s="3"/>
-      <c r="C171" s="3"/>
-      <c r="D171" s="3"/>
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171" s="5" t="s">
+        <v>346</v>
+      </c>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="3"/>
@@ -7628,10 +7781,18 @@
       <c r="Z171" s="3"/>
     </row>
     <row r="172" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="3"/>
-      <c r="B172" s="3"/>
-      <c r="C172" s="3"/>
-      <c r="D172" s="3"/>
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D172" s="5" t="s">
+        <v>347</v>
+      </c>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="3"/>
@@ -7656,10 +7817,18 @@
       <c r="Z172" s="3"/>
     </row>
     <row r="173" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="3"/>
-      <c r="B173" s="3"/>
-      <c r="C173" s="3"/>
-      <c r="D173" s="3"/>
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="C173" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D173" s="15" t="s">
+        <v>348</v>
+      </c>
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
       <c r="G173" s="3"/>
@@ -7684,10 +7853,18 @@
       <c r="Z173" s="3"/>
     </row>
     <row r="174" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="3"/>
-      <c r="B174" s="3"/>
-      <c r="C174" s="3"/>
-      <c r="D174" s="3"/>
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D174" s="5" t="s">
+        <v>359</v>
+      </c>
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
       <c r="G174" s="3"/>
@@ -7739,7 +7916,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
     </row>
-    <row r="176" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -7767,7 +7944,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
     </row>
-    <row r="177" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -7795,7 +7972,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
     </row>
-    <row r="178" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -7823,7 +8000,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
     </row>
-    <row r="179" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -7851,7 +8028,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
     </row>
-    <row r="180" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -7879,7 +8056,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
     </row>
-    <row r="181" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -7907,7 +8084,7 @@
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
     </row>
-    <row r="182" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -7935,7 +8112,7 @@
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
     </row>
-    <row r="183" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -7963,7 +8140,7 @@
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
     </row>
-    <row r="184" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -7991,7 +8168,7 @@
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
     </row>
-    <row r="185" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -8019,7 +8196,7 @@
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
     </row>
-    <row r="186" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -8047,7 +8224,7 @@
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
     </row>
-    <row r="187" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -8075,7 +8252,7 @@
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
     </row>
-    <row r="188" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -8103,7 +8280,7 @@
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
     </row>
-    <row r="189" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -8131,7 +8308,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
     </row>
-    <row r="190" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -8159,7 +8336,7 @@
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
     </row>
-    <row r="191" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -8187,7 +8364,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
     </row>
-    <row r="192" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -8215,7 +8392,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
     </row>
-    <row r="193" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -8243,7 +8420,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
     </row>
-    <row r="194" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -8271,7 +8448,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
     </row>
-    <row r="195" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -8299,7 +8476,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
     </row>
-    <row r="196" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -8327,7 +8504,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
     </row>
-    <row r="197" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -8355,7 +8532,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
     </row>
-    <row r="198" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -8383,7 +8560,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
     </row>
-    <row r="199" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -8411,7 +8588,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
     </row>
-    <row r="200" spans="1:26" ht="12.45" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -30876,5 +31053,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/assets/data/capcollection.xlsx
+++ b/assets/data/capcollection.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\BottleCapCollection\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB5EB31-0257-4AC1-AB5A-EDBC90A9BDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC6D2D7-A24C-44D1-8EF9-C70A2DC4DD94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="367">
   <si>
     <t>FONT D'OR</t>
   </si>
@@ -274,9 +274,6 @@
     <t>PAULANER (München)</t>
   </si>
   <si>
-    <t>DESPERADOS</t>
-  </si>
-  <si>
     <t>PAULANER 
 (Original Münchner Hell)</t>
   </si>
@@ -1129,6 +1126,27 @@
   </si>
   <si>
     <t>SVIJANY (maz)</t>
+  </si>
+  <si>
+    <t>image174.png</t>
+  </si>
+  <si>
+    <t>image175.png</t>
+  </si>
+  <si>
+    <t>image176.png</t>
+  </si>
+  <si>
+    <t>DESPERADOS ORIGINAL</t>
+  </si>
+  <si>
+    <t>DESPERADOS MOJITO</t>
+  </si>
+  <si>
+    <t>FUZETEA</t>
+  </si>
+  <si>
+    <t>CLAUSTHALER (non-alcoholic)</t>
   </si>
 </sst>
 </file>
@@ -1208,7 +1226,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1259,11 +1277,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1308,6 +1341,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1631,16 +1670,16 @@
   <sheetData>
     <row r="1" spans="1:26" ht="13.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>142</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -1675,7 +1714,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -1711,7 +1750,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1747,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -1783,7 +1822,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -1819,7 +1858,7 @@
         <v>13</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -1855,7 +1894,7 @@
         <v>13</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -1891,7 +1930,7 @@
         <v>13</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -1927,7 +1966,7 @@
         <v>13</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -1963,7 +2002,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -1999,7 +2038,7 @@
         <v>13</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -2035,7 +2074,7 @@
         <v>13</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -2071,7 +2110,7 @@
         <v>13</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -2107,7 +2146,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -2142,7 +2181,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -2178,7 +2217,7 @@
         <v>13</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -2214,7 +2253,7 @@
         <v>13</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -2250,7 +2289,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -2286,7 +2325,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -2322,7 +2361,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -2352,13 +2391,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="D21" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -2387,16 +2426,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="6"/>
@@ -2425,13 +2464,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="D23" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
@@ -2461,13 +2500,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -2497,13 +2536,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -2533,13 +2572,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -2569,13 +2608,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -2605,13 +2644,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
@@ -2641,13 +2680,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -2677,13 +2716,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -2713,13 +2752,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -2749,13 +2788,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
@@ -2791,7 +2830,7 @@
         <v>11</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
@@ -2821,13 +2860,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
@@ -2857,13 +2896,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
@@ -2893,13 +2932,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
@@ -2935,7 +2974,7 @@
         <v>13</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
@@ -2965,13 +3004,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -3007,7 +3046,7 @@
         <v>13</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
@@ -3037,13 +3076,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="D40" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
@@ -3073,13 +3112,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
@@ -3115,7 +3154,7 @@
         <v>13</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
@@ -3151,7 +3190,7 @@
         <v>13</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
@@ -3181,13 +3220,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
@@ -3223,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
@@ -3253,16 +3292,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="6"/>
@@ -3297,7 +3336,7 @@
         <v>13</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
@@ -3333,7 +3372,7 @@
         <v>13</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
@@ -3369,7 +3408,7 @@
         <v>13</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
@@ -3399,13 +3438,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
@@ -3435,13 +3474,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
@@ -3477,7 +3516,7 @@
         <v>13</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
@@ -3513,7 +3552,7 @@
         <v>13</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
@@ -3549,7 +3588,7 @@
         <v>13</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
@@ -3585,7 +3624,7 @@
         <v>13</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
@@ -3621,7 +3660,7 @@
         <v>13</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -3657,7 +3696,7 @@
         <v>13</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -3693,7 +3732,7 @@
         <v>13</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -3723,13 +3762,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>134</v>
-      </c>
       <c r="D59" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
@@ -3759,13 +3798,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
@@ -3795,13 +3834,13 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
@@ -3831,13 +3870,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
@@ -3867,13 +3906,13 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C63" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>92</v>
-      </c>
       <c r="D63" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
@@ -3909,7 +3948,7 @@
         <v>13</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -3945,7 +3984,7 @@
         <v>13</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
@@ -3981,7 +4020,7 @@
         <v>13</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
@@ -4017,7 +4056,7 @@
         <v>13</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
@@ -4053,7 +4092,7 @@
         <v>13</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
@@ -4088,7 +4127,7 @@
         <v>13</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
@@ -4123,7 +4162,7 @@
         <v>13</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
@@ -4159,7 +4198,7 @@
         <v>13</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
@@ -4195,7 +4234,7 @@
         <v>13</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -4225,13 +4264,13 @@
         <v>72</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
@@ -4260,13 +4299,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -4302,7 +4341,7 @@
         <v>13</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
@@ -4338,10 +4377,10 @@
         <v>13</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="6"/>
@@ -4376,7 +4415,7 @@
         <v>13</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -4412,7 +4451,7 @@
         <v>13</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -4448,7 +4487,7 @@
         <v>13</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -4478,13 +4517,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
@@ -4520,7 +4559,7 @@
         <v>13</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -4556,7 +4595,7 @@
         <v>13</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
@@ -4592,7 +4631,7 @@
         <v>13</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -4628,7 +4667,7 @@
         <v>13</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -4664,7 +4703,7 @@
         <v>13</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
@@ -4700,7 +4739,7 @@
         <v>13</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
@@ -4736,7 +4775,7 @@
         <v>13</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
@@ -4772,7 +4811,7 @@
         <v>13</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
@@ -4808,7 +4847,7 @@
         <v>13</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -4844,7 +4883,7 @@
         <v>13</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -4880,7 +4919,7 @@
         <v>13</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -4910,13 +4949,13 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
@@ -4952,7 +4991,7 @@
         <v>13</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
@@ -4988,7 +5027,7 @@
         <v>13</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
@@ -5024,7 +5063,7 @@
         <v>13</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
@@ -5060,7 +5099,7 @@
         <v>13</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
@@ -5090,13 +5129,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
@@ -5126,13 +5165,13 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
@@ -5168,7 +5207,7 @@
         <v>13</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
@@ -5204,7 +5243,7 @@
         <v>13</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
@@ -5234,13 +5273,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
@@ -5270,13 +5309,13 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
@@ -5306,13 +5345,13 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
@@ -5348,7 +5387,7 @@
         <v>13</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
@@ -5383,7 +5422,7 @@
         <v>1</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
@@ -5418,7 +5457,7 @@
         <v>1</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
@@ -5447,13 +5486,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
@@ -5489,7 +5528,7 @@
         <v>13</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
@@ -5519,13 +5558,13 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
@@ -5561,7 +5600,7 @@
         <v>13</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
@@ -5596,7 +5635,7 @@
         <v>1</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
@@ -5632,7 +5671,7 @@
         <v>13</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
@@ -5662,13 +5701,13 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
@@ -5704,7 +5743,7 @@
         <v>13</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
@@ -5734,13 +5773,13 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
@@ -5770,13 +5809,13 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
@@ -5806,13 +5845,13 @@
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="3"/>
@@ -5848,7 +5887,7 @@
         <v>13</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" s="3"/>
@@ -5878,13 +5917,13 @@
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>79</v>
+        <v>363</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
@@ -5914,13 +5953,13 @@
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
@@ -5950,13 +5989,13 @@
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E121" s="3"/>
       <c r="F121" s="3"/>
@@ -5986,13 +6025,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E122" s="3"/>
       <c r="F122" s="3"/>
@@ -6022,13 +6061,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
@@ -6058,13 +6097,13 @@
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
@@ -6100,7 +6139,7 @@
         <v>1</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E125" s="3"/>
       <c r="F125" s="3"/>
@@ -6130,13 +6169,13 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E126" s="3"/>
       <c r="F126" s="3"/>
@@ -6166,13 +6205,13 @@
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
@@ -6202,13 +6241,13 @@
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
@@ -6237,13 +6276,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C129" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E129" s="3"/>
       <c r="F129" s="3"/>
@@ -6273,13 +6312,13 @@
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C130" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E130" s="3"/>
       <c r="F130" s="3"/>
@@ -6309,13 +6348,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
@@ -6345,13 +6384,13 @@
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
@@ -6381,13 +6420,13 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E133" s="3"/>
       <c r="F133" s="3"/>
@@ -6417,13 +6456,13 @@
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
@@ -6453,13 +6492,13 @@
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C135" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
@@ -6489,13 +6528,13 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C136" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
@@ -6525,13 +6564,13 @@
         <v>136</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C137" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E137" s="3"/>
       <c r="F137" s="3"/>
@@ -6561,13 +6600,13 @@
         <v>137</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E138" s="3"/>
       <c r="F138" s="3"/>
@@ -6597,13 +6636,13 @@
         <v>138</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C139" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
@@ -6633,13 +6672,13 @@
         <v>139</v>
       </c>
       <c r="B140" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C140" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="C140" s="4" t="s">
+      <c r="D140" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>279</v>
       </c>
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
@@ -6669,13 +6708,13 @@
         <v>140</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C141" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E141" s="3"/>
       <c r="F141" s="3"/>
@@ -6705,13 +6744,13 @@
         <v>141</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C142" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="E142" s="3"/>
       <c r="F142" s="3"/>
@@ -6741,13 +6780,13 @@
         <v>142</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C143" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
@@ -6777,13 +6816,13 @@
         <v>143</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C144" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
@@ -6813,13 +6852,13 @@
         <v>144</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C145" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
@@ -6849,13 +6888,13 @@
         <v>145</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C146" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E146" s="3"/>
       <c r="F146" s="3"/>
@@ -6885,13 +6924,13 @@
         <v>146</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C147" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
@@ -6921,13 +6960,13 @@
         <v>147</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
@@ -6957,13 +6996,13 @@
         <v>148</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E149" s="3"/>
       <c r="F149" s="3"/>
@@ -6993,13 +7032,13 @@
         <v>149</v>
       </c>
       <c r="B150" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="C150" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D150" s="5" t="s">
         <v>299</v>
-      </c>
-      <c r="C150" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>300</v>
       </c>
       <c r="E150" s="3"/>
       <c r="F150" s="3"/>
@@ -7029,13 +7068,13 @@
         <v>150</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C151" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
@@ -7065,13 +7104,13 @@
         <v>151</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
@@ -7101,13 +7140,13 @@
         <v>152</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E153" s="3"/>
       <c r="F153" s="3"/>
@@ -7137,13 +7176,13 @@
         <v>153</v>
       </c>
       <c r="B154" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C154" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="C154" s="4" t="s">
-        <v>314</v>
-      </c>
       <c r="D154" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E154" s="3"/>
       <c r="F154" s="12"/>
@@ -7173,13 +7212,13 @@
         <v>154</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
@@ -7209,13 +7248,13 @@
         <v>155</v>
       </c>
       <c r="B156" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="C156" s="4" t="s">
         <v>316</v>
       </c>
-      <c r="C156" s="4" t="s">
-        <v>317</v>
-      </c>
       <c r="D156" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
@@ -7245,13 +7284,13 @@
         <v>156</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C157" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E157" s="3"/>
       <c r="F157" s="3"/>
@@ -7281,13 +7320,13 @@
         <v>157</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E158" s="3"/>
       <c r="F158" s="3"/>
@@ -7317,13 +7356,13 @@
         <v>158</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
@@ -7353,13 +7392,13 @@
         <v>159</v>
       </c>
       <c r="B160" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D160" s="5" t="s">
         <v>320</v>
-      </c>
-      <c r="C160" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="D160" s="5" t="s">
-        <v>321</v>
       </c>
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
@@ -7389,13 +7428,13 @@
         <v>160</v>
       </c>
       <c r="B161" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D161" s="5" t="s">
         <v>322</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D161" s="5" t="s">
-        <v>323</v>
       </c>
       <c r="E161" s="3"/>
       <c r="F161" s="3"/>
@@ -7425,13 +7464,13 @@
         <v>161</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C162" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E162" s="3"/>
       <c r="F162" s="3"/>
@@ -7461,13 +7500,13 @@
         <v>162</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
@@ -7497,13 +7536,13 @@
         <v>163</v>
       </c>
       <c r="B164" s="14" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C164" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
@@ -7533,13 +7572,13 @@
         <v>164</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E165" s="3"/>
       <c r="F165" s="3"/>
@@ -7569,13 +7608,13 @@
         <v>165</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C166" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E166" s="3"/>
       <c r="F166" s="3"/>
@@ -7605,13 +7644,13 @@
         <v>166</v>
       </c>
       <c r="B167" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
@@ -7641,13 +7680,13 @@
         <v>167</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C168" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
@@ -7677,13 +7716,13 @@
         <v>168</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C169" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E169" s="3"/>
       <c r="F169" s="3"/>
@@ -7713,13 +7752,13 @@
         <v>169</v>
       </c>
       <c r="B170" s="14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C170" s="14" t="s">
         <v>13</v>
       </c>
       <c r="D170" s="15" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E170" s="3"/>
       <c r="F170" s="3"/>
@@ -7749,13 +7788,13 @@
         <v>170</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C171" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
@@ -7785,13 +7824,13 @@
         <v>171</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C172" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
@@ -7821,13 +7860,13 @@
         <v>172</v>
       </c>
       <c r="B173" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C173" s="14" t="s">
         <v>13</v>
       </c>
       <c r="D173" s="15" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E173" s="3"/>
       <c r="F173" s="3"/>
@@ -7857,13 +7896,13 @@
         <v>173</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C174" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E174" s="3"/>
       <c r="F174" s="3"/>
@@ -7889,10 +7928,18 @@
       <c r="Z174" s="3"/>
     </row>
     <row r="175" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="3"/>
-      <c r="B175" s="3"/>
-      <c r="C175" s="3"/>
-      <c r="D175" s="3"/>
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="C175" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D175" s="15" t="s">
+        <v>360</v>
+      </c>
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="3"/>
@@ -7917,10 +7964,18 @@
       <c r="Z175" s="3"/>
     </row>
     <row r="176" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="3"/>
-      <c r="B176" s="3"/>
-      <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="C176" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D176" s="15" t="s">
+        <v>361</v>
+      </c>
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
       <c r="G176" s="3"/>
@@ -7945,10 +8000,18 @@
       <c r="Z176" s="3"/>
     </row>
     <row r="177" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="3"/>
-      <c r="B177" s="3"/>
-      <c r="C177" s="3"/>
-      <c r="D177" s="3"/>
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="C177" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D177" s="17" t="s">
+        <v>362</v>
+      </c>
       <c r="E177" s="3"/>
       <c r="F177" s="3"/>
       <c r="G177" s="3"/>

--- a/assets/data/capcollection.xlsx
+++ b/assets/data/capcollection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\BottleCapCollection\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC6D2D7-A24C-44D1-8EF9-C70A2DC4DD94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E630D34C-CA41-4686-917D-81782C927DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="371">
   <si>
     <t>FONT D'OR</t>
   </si>
@@ -1147,6 +1147,18 @@
   </si>
   <si>
     <t>CLAUSTHALER (non-alcoholic)</t>
+  </si>
+  <si>
+    <t>image177.png</t>
+  </si>
+  <si>
+    <t>image178.png</t>
+  </si>
+  <si>
+    <t>DAURA DAMM (1876)</t>
+  </si>
+  <si>
+    <t>FALKE SIN</t>
   </si>
 </sst>
 </file>
@@ -8036,10 +8048,18 @@
       <c r="Z177" s="3"/>
     </row>
     <row r="178" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="3"/>
-      <c r="B178" s="3"/>
-      <c r="C178" s="3"/>
-      <c r="D178" s="3"/>
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="C178" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D178" s="15" t="s">
+        <v>367</v>
+      </c>
       <c r="E178" s="3"/>
       <c r="F178" s="3"/>
       <c r="G178" s="3"/>
@@ -8064,10 +8084,18 @@
       <c r="Z178" s="3"/>
     </row>
     <row r="179" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="3"/>
-      <c r="B179" s="3"/>
-      <c r="C179" s="3"/>
-      <c r="D179" s="3"/>
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="C179" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D179" s="17" t="s">
+        <v>368</v>
+      </c>
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
       <c r="G179" s="3"/>

--- a/assets/data/capcollection.xlsx
+++ b/assets/data/capcollection.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maria\Desktop\PROGRAMES\BottleCapCollection\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E630D34C-CA41-4686-917D-81782C927DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF9279E2-CD5A-470A-9F10-736464D64725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="383">
   <si>
     <t>FONT D'OR</t>
   </si>
@@ -1159,6 +1159,43 @@
   </si>
   <si>
     <t>FALKE SIN</t>
+  </si>
+  <si>
+    <t>image179.png</t>
+  </si>
+  <si>
+    <t>image180.png</t>
+  </si>
+  <si>
+    <t>image181.png</t>
+  </si>
+  <si>
+    <t>image182.png</t>
+  </si>
+  <si>
+    <t>image183.png</t>
+  </si>
+  <si>
+    <t>image184.png</t>
+  </si>
+  <si>
+    <t>COCA-COLA (zero) v2</t>
+  </si>
+  <si>
+    <t>AMSTEL (oro 0,0)</t>
+  </si>
+  <si>
+    <t>HEINEKEN (original)</t>
+  </si>
+  <si>
+    <t>HEINEKEN (0.0)</t>
+  </si>
+  <si>
+    <t>SCHWEPPES (limón)</t>
+  </si>
+  <si>
+    <t>CRUZCAMPO 
+(especial sin gluten)</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1360,6 +1397,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8120,10 +8160,18 @@
       <c r="Z179" s="3"/>
     </row>
     <row r="180" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="3"/>
-      <c r="B180" s="3"/>
-      <c r="C180" s="3"/>
-      <c r="D180" s="3"/>
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="C180" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D180" s="15" t="s">
+        <v>371</v>
+      </c>
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
       <c r="G180" s="3"/>
@@ -8148,10 +8196,18 @@
       <c r="Z180" s="3"/>
     </row>
     <row r="181" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="3"/>
-      <c r="B181" s="3"/>
-      <c r="C181" s="3"/>
-      <c r="D181" s="3"/>
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="C181" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D181" s="17" t="s">
+        <v>372</v>
+      </c>
       <c r="E181" s="3"/>
       <c r="F181" s="3"/>
       <c r="G181" s="3"/>
@@ -8176,10 +8232,18 @@
       <c r="Z181" s="3"/>
     </row>
     <row r="182" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="3"/>
-      <c r="B182" s="3"/>
-      <c r="C182" s="3"/>
-      <c r="D182" s="3"/>
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="C182" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D182" s="15" t="s">
+        <v>373</v>
+      </c>
       <c r="E182" s="3"/>
       <c r="F182" s="3"/>
       <c r="G182" s="3"/>
@@ -8204,10 +8268,18 @@
       <c r="Z182" s="3"/>
     </row>
     <row r="183" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="3"/>
-      <c r="B183" s="3"/>
-      <c r="C183" s="3"/>
-      <c r="D183" s="3"/>
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="C183" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D183" s="17" t="s">
+        <v>374</v>
+      </c>
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
       <c r="G183" s="3"/>
@@ -8232,10 +8304,18 @@
       <c r="Z183" s="3"/>
     </row>
     <row r="184" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="3"/>
-      <c r="B184" s="3"/>
-      <c r="C184" s="3"/>
-      <c r="D184" s="3"/>
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="C184" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D184" s="15" t="s">
+        <v>375</v>
+      </c>
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
       <c r="G184" s="3"/>
@@ -8260,10 +8340,18 @@
       <c r="Z184" s="3"/>
     </row>
     <row r="185" spans="1:26" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="3"/>
-      <c r="B185" s="3"/>
-      <c r="C185" s="3"/>
-      <c r="D185" s="3"/>
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="C185" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D185" s="17" t="s">
+        <v>376</v>
+      </c>
       <c r="E185" s="3"/>
       <c r="F185" s="3"/>
       <c r="G185" s="3"/>
